--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run3/epoch_140/per_file_predictions_epoch_140.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run3/epoch_140/per_file_predictions_epoch_140.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="523">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,781 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.8750,0.0295,0.0600,0.0198</t>
-  </si>
-  <si>
-    <t>0.0067,0.0007,0.0002,0.9975</t>
-  </si>
-  <si>
-    <t>0.1750,0.0205,0.0105,0.8973</t>
-  </si>
-  <si>
-    <t>0.1991,0.0020,0.0016,0.9294</t>
-  </si>
-  <si>
-    <t>0.9969,0.0015,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9923,0.0009,0.0002,0.0040</t>
-  </si>
-  <si>
-    <t>0.9941,0.0032,0.0006,0.0006</t>
-  </si>
-  <si>
-    <t>0.9952,0.0036,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.9885,0.0103,0.0011,0.0009</t>
-  </si>
-  <si>
-    <t>0.9947,0.0015,0.0003,0.0011</t>
-  </si>
-  <si>
-    <t>0.9982,0.0007,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9933,0.0029,0.0005,0.0009</t>
-  </si>
-  <si>
-    <t>0.6922,0.0186,0.3117,0.0095</t>
-  </si>
-  <si>
-    <t>0.4297,0.0131,0.6347,0.0028</t>
-  </si>
-  <si>
-    <t>0.3510,0.0051,0.7558,0.0017</t>
-  </si>
-  <si>
-    <t>0.2788,0.0097,0.7707,0.0019</t>
-  </si>
-  <si>
-    <t>0.6452,0.0568,0.3393,0.0166</t>
-  </si>
-  <si>
-    <t>0.0049,0.9917,0.0028,0.0001</t>
-  </si>
-  <si>
-    <t>0.0075,0.9895,0.0027,0.0001</t>
-  </si>
-  <si>
-    <t>0.3564,0.6845,0.0289,0.0020</t>
-  </si>
-  <si>
-    <t>0.0418,0.9621,0.0026,0.0007</t>
-  </si>
-  <si>
-    <t>0.0031,0.9945,0.0013,0.0001</t>
-  </si>
-  <si>
-    <t>0.6339,0.0096,0.3867,0.0112</t>
-  </si>
-  <si>
-    <t>0.5663,0.0162,0.4567,0.0154</t>
-  </si>
-  <si>
-    <t>0.0359,0.0022,0.9721,0.0025</t>
-  </si>
-  <si>
-    <t>0.2117,0.0073,0.7731,0.0371</t>
-  </si>
-  <si>
-    <t>0.1059,0.0047,0.9238,0.0056</t>
-  </si>
-  <si>
-    <t>0.2606,0.0074,0.7998,0.0107</t>
-  </si>
-  <si>
-    <t>0.0098,0.0024,0.9856,0.0032</t>
-  </si>
-  <si>
-    <t>0.8244,0.1796,0.0266,0.0053</t>
-  </si>
-  <si>
-    <t>0.5255,0.2269,0.3292,0.0158</t>
-  </si>
-  <si>
-    <t>0.0009,0.0109,0.9877,0.0183</t>
-  </si>
-  <si>
-    <t>0.0129,0.9548,0.0691,0.0027</t>
-  </si>
-  <si>
-    <t>0.5449,0.4514,0.1181,0.0285</t>
-  </si>
-  <si>
-    <t>0.3908,0.1215,0.5047,0.0171</t>
-  </si>
-  <si>
-    <t>0.9150,0.0692,0.0259,0.0033</t>
-  </si>
-  <si>
-    <t>0.0211,0.9222,0.4215,0.0029</t>
-  </si>
-  <si>
-    <t>0.0042,0.9347,0.2593,0.0075</t>
-  </si>
-  <si>
-    <t>0.0410,0.1484,0.9151,0.0026</t>
-  </si>
-  <si>
-    <t>0.1034,0.0243,0.8769,0.0148</t>
-  </si>
-  <si>
-    <t>0.2361,0.0058,0.7551,0.0229</t>
-  </si>
-  <si>
-    <t>0.0159,0.0381,0.9602,0.0012</t>
-  </si>
-  <si>
-    <t>0.0034,0.9868,0.0338,0.0003</t>
-  </si>
-  <si>
-    <t>0.1044,0.0553,0.8377,0.0504</t>
-  </si>
-  <si>
-    <t>0.0794,0.2133,0.0426,0.9266</t>
-  </si>
-  <si>
-    <t>0.0098,0.9260,0.0222,0.3123</t>
-  </si>
-  <si>
-    <t>0.0096,0.9666,0.0934,0.0015</t>
-  </si>
-  <si>
-    <t>0.0014,0.9839,0.1945,0.0047</t>
-  </si>
-  <si>
-    <t>0.0092,0.0624,0.9677,0.0087</t>
-  </si>
-  <si>
-    <t>0.0214,0.1590,0.9124,0.0013</t>
-  </si>
-  <si>
-    <t>0.2408,0.0101,0.7864,0.0196</t>
-  </si>
-  <si>
-    <t>0.0227,0.0012,0.9821,0.0021</t>
-  </si>
-  <si>
-    <t>0.0071,0.0075,0.9853,0.0044</t>
-  </si>
-  <si>
-    <t>0.0042,0.0226,0.9881,0.0011</t>
-  </si>
-  <si>
-    <t>0.9767,0.0243,0.0024,0.0010</t>
-  </si>
-  <si>
-    <t>0.9455,0.0769,0.0062,0.0007</t>
-  </si>
-  <si>
-    <t>0.9576,0.0487,0.0053,0.0012</t>
-  </si>
-  <si>
-    <t>0.0044,0.1223,0.9855,0.0021</t>
-  </si>
-  <si>
-    <t>0.9863,0.0030,0.0003,0.0045</t>
-  </si>
-  <si>
-    <t>0.9892,0.0069,0.0018,0.0011</t>
-  </si>
-  <si>
-    <t>0.9871,0.0092,0.0020,0.0005</t>
-  </si>
-  <si>
-    <t>0.0006,0.9693,0.7142,0.0002</t>
-  </si>
-  <si>
-    <t>0.0049,0.0142,0.9912,0.0008</t>
-  </si>
-  <si>
-    <t>0.0215,0.0213,0.9339,0.0417</t>
-  </si>
-  <si>
-    <t>0.0005,0.8291,0.9725,0.0001</t>
-  </si>
-  <si>
-    <t>0.0057,0.0086,0.9896,0.0014</t>
-  </si>
-  <si>
-    <t>0.0465,0.8490,0.1996,0.0042</t>
-  </si>
-  <si>
-    <t>0.0041,0.9918,0.0012,0.0001</t>
-  </si>
-  <si>
-    <t>0.2570,0.1206,0.7348,0.0107</t>
-  </si>
-  <si>
-    <t>0.1673,0.5255,0.3265,0.0027</t>
-  </si>
-  <si>
-    <t>0.0075,0.0358,0.9794,0.0030</t>
-  </si>
-  <si>
-    <t>0.0008,0.8405,0.9196,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.9130,0.8906,0.0000</t>
-  </si>
-  <si>
-    <t>0.0046,0.9771,0.1515,0.0005</t>
-  </si>
-  <si>
-    <t>0.0004,0.9504,0.7192,0.0010</t>
-  </si>
-  <si>
-    <t>0.0370,0.0004,0.0034,0.9760</t>
-  </si>
-  <si>
-    <t>0.0045,0.0066,0.0005,0.9974</t>
-  </si>
-  <si>
-    <t>0.0067,0.0133,0.0071,0.9916</t>
-  </si>
-  <si>
-    <t>0.0055,0.0002,0.0003,0.9974</t>
-  </si>
-  <si>
-    <t>0.0012,0.0018,0.0026,0.9979</t>
-  </si>
-  <si>
-    <t>0.0035,0.0052,0.0013,0.9972</t>
-  </si>
-  <si>
-    <t>0.0062,0.8551,0.7174,0.0009</t>
-  </si>
-  <si>
-    <t>0.0015,0.6290,0.9748,0.0004</t>
-  </si>
-  <si>
-    <t>0.0086,0.5576,0.8801,0.0018</t>
-  </si>
-  <si>
-    <t>0.0259,0.1222,0.9282,0.0060</t>
-  </si>
-  <si>
-    <t>0.0003,0.9577,0.5386,0.0000</t>
-  </si>
-  <si>
-    <t>0.0019,0.7808,0.9286,0.0007</t>
-  </si>
-  <si>
-    <t>0.9943,0.0038,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.9761,0.0306,0.0026,0.0005</t>
-  </si>
-  <si>
-    <t>0.9701,0.0301,0.0044,0.0010</t>
-  </si>
-  <si>
-    <t>0.9802,0.0100,0.0031,0.0039</t>
-  </si>
-  <si>
-    <t>0.9713,0.0213,0.0037,0.0026</t>
-  </si>
-  <si>
-    <t>0.9948,0.0037,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.9876,0.0093,0.0020,0.0006</t>
-  </si>
-  <si>
-    <t>0.9822,0.0213,0.0025,0.0002</t>
-  </si>
-  <si>
-    <t>0.9954,0.0010,0.0001,0.0011</t>
-  </si>
-  <si>
-    <t>0.9932,0.0032,0.0013,0.0006</t>
-  </si>
-  <si>
-    <t>0.9955,0.0019,0.0004,0.0005</t>
-  </si>
-  <si>
-    <t>0.9939,0.0013,0.0004,0.0012</t>
-  </si>
-  <si>
-    <t>0.9923,0.0042,0.0009,0.0007</t>
-  </si>
-  <si>
-    <t>0.9878,0.0055,0.0020,0.0018</t>
-  </si>
-  <si>
-    <t>0.9899,0.0050,0.0011,0.0012</t>
-  </si>
-  <si>
-    <t>0.9908,0.0027,0.0006,0.0021</t>
-  </si>
-  <si>
-    <t>0.0005,0.0018,0.9858,0.0353</t>
-  </si>
-  <si>
-    <t>0.1198,0.0289,0.8872,0.0063</t>
-  </si>
-  <si>
-    <t>0.4413,0.0074,0.5261,0.0386</t>
-  </si>
-  <si>
-    <t>0.1359,0.0022,0.9128,0.0024</t>
-  </si>
-  <si>
-    <t>0.0642,0.9459,0.0037,0.0003</t>
-  </si>
-  <si>
-    <t>0.1188,0.8600,0.0615,0.0021</t>
-  </si>
-  <si>
-    <t>0.1773,0.8634,0.0106,0.0004</t>
-  </si>
-  <si>
-    <t>0.1431,0.8666,0.0083,0.0035</t>
-  </si>
-  <si>
-    <t>0.0636,0.9332,0.0121,0.0007</t>
-  </si>
-  <si>
-    <t>0.0477,0.9574,0.0035,0.0003</t>
-  </si>
-  <si>
-    <t>0.6667,0.4417,0.0034,0.0013</t>
-  </si>
-  <si>
-    <t>0.6843,0.1155,0.1974,0.0462</t>
-  </si>
-  <si>
-    <t>0.2581,0.0094,0.7961,0.0114</t>
-  </si>
-  <si>
-    <t>0.3881,0.2074,0.4636,0.0332</t>
-  </si>
-  <si>
-    <t>0.4747,0.1919,0.3466,0.0625</t>
-  </si>
-  <si>
-    <t>0.0388,0.0588,0.0272,0.9626</t>
-  </si>
-  <si>
-    <t>0.0013,0.9918,0.0137,0.0029</t>
-  </si>
-  <si>
-    <t>0.0004,0.9946,0.0355,0.0010</t>
-  </si>
-  <si>
-    <t>0.0296,0.9078,0.0465,0.1759</t>
-  </si>
-  <si>
-    <t>0.0007,0.9733,0.7540,0.0002</t>
-  </si>
-  <si>
-    <t>0.0122,0.9805,0.0365,0.0002</t>
-  </si>
-  <si>
-    <t>0.5144,0.5499,0.0478,0.0048</t>
-  </si>
-  <si>
-    <t>0.7212,0.3472,0.0230,0.0015</t>
-  </si>
-  <si>
-    <t>0.9052,0.1077,0.0139,0.0074</t>
-  </si>
-  <si>
-    <t>0.9669,0.0165,0.0109,0.0036</t>
-  </si>
-  <si>
-    <t>0.9826,0.0022,0.0012,0.0099</t>
-  </si>
-  <si>
-    <t>0.9615,0.0300,0.0114,0.0025</t>
-  </si>
-  <si>
-    <t>0.9891,0.0046,0.0013,0.0019</t>
-  </si>
-  <si>
-    <t>0.8066,0.1852,0.0523,0.0060</t>
-  </si>
-  <si>
-    <t>0.9781,0.0068,0.0019,0.0066</t>
-  </si>
-  <si>
-    <t>0.9522,0.0204,0.0101,0.0108</t>
-  </si>
-  <si>
-    <t>0.0135,0.5591,0.8295,0.0011</t>
-  </si>
-  <si>
-    <t>0.0212,0.2643,0.8705,0.0008</t>
-  </si>
-  <si>
-    <t>0.0139,0.7941,0.5709,0.0036</t>
-  </si>
-  <si>
-    <t>0.0107,0.4154,0.8356,0.0006</t>
-  </si>
-  <si>
-    <t>0.6006,0.0764,0.3666,0.0396</t>
-  </si>
-  <si>
-    <t>0.2786,0.6584,0.0678,0.0779</t>
-  </si>
-  <si>
-    <t>0.4519,0.0157,0.6379,0.0060</t>
-  </si>
-  <si>
-    <t>0.5228,0.0664,0.4318,0.0548</t>
-  </si>
-  <si>
-    <t>0.0290,0.0028,0.0093,0.9776</t>
-  </si>
-  <si>
-    <t>0.0018,0.0006,0.0007,0.9985</t>
-  </si>
-  <si>
-    <t>0.0112,0.0613,0.0052,0.9898</t>
-  </si>
-  <si>
-    <t>0.0311,0.0010,0.0420,0.9389</t>
-  </si>
-  <si>
-    <t>0.0006,0.9631,0.6204,0.0003</t>
-  </si>
-  <si>
-    <t>0.9725,0.0137,0.0049,0.0055</t>
-  </si>
-  <si>
-    <t>0.3051,0.7473,0.0125,0.0040</t>
-  </si>
-  <si>
-    <t>0.9559,0.0257,0.0037,0.0119</t>
-  </si>
-  <si>
-    <t>0.8300,0.2170,0.0183,0.0028</t>
-  </si>
-  <si>
-    <t>0.9697,0.0058,0.0119,0.0061</t>
-  </si>
-  <si>
-    <t>0.5302,0.0558,0.0082,0.5494</t>
-  </si>
-  <si>
-    <t>0.9793,0.0084,0.0027,0.0037</t>
-  </si>
-  <si>
-    <t>0.0025,0.0115,0.9728,0.0566</t>
-  </si>
-  <si>
-    <t>0.6278,0.0027,0.0150,0.3754</t>
-  </si>
-  <si>
-    <t>0.7370,0.0026,0.0203,0.1656</t>
-  </si>
-  <si>
-    <t>0.6320,0.3852,0.0552,0.0138</t>
-  </si>
-  <si>
-    <t>0.9222,0.0448,0.0186,0.0038</t>
-  </si>
-  <si>
-    <t>0.6733,0.0907,0.2796,0.0129</t>
-  </si>
-  <si>
-    <t>0.5694,0.3386,0.0885,0.0647</t>
-  </si>
-  <si>
-    <t>0.5160,0.4634,0.1074,0.0059</t>
-  </si>
-  <si>
-    <t>0.7378,0.2389,0.0583,0.0048</t>
-  </si>
-  <si>
-    <t>0.9890,0.0017,0.0004,0.0049</t>
-  </si>
-  <si>
-    <t>0.9861,0.0062,0.0021,0.0024</t>
-  </si>
-  <si>
-    <t>0.9899,0.0031,0.0012,0.0023</t>
-  </si>
-  <si>
-    <t>0.9630,0.0033,0.0053,0.0213</t>
-  </si>
-  <si>
-    <t>0.9616,0.0051,0.0138,0.0083</t>
-  </si>
-  <si>
-    <t>0.9622,0.0239,0.0088,0.0056</t>
-  </si>
-  <si>
-    <t>0.9851,0.0023,0.0005,0.0097</t>
-  </si>
-  <si>
-    <t>0.9814,0.0078,0.0027,0.0040</t>
-  </si>
-  <si>
-    <t>0.7084,0.3815,0.0050,0.0025</t>
-  </si>
-  <si>
-    <t>0.7064,0.3604,0.0202,0.0007</t>
-  </si>
-  <si>
-    <t>0.6132,0.5034,0.0119,0.0008</t>
-  </si>
-  <si>
-    <t>0.0822,0.3058,0.8145,0.0100</t>
-  </si>
-  <si>
-    <t>0.9549,0.0338,0.0088,0.0038</t>
-  </si>
-  <si>
-    <t>0.8985,0.1006,0.0180,0.0063</t>
-  </si>
-  <si>
-    <t>0.9319,0.0666,0.0138,0.0008</t>
-  </si>
-  <si>
-    <t>0.8965,0.0997,0.0242,0.0073</t>
-  </si>
-  <si>
-    <t>0.0033,0.0186,0.9925,0.0022</t>
-  </si>
-  <si>
-    <t>0.9659,0.0238,0.0046,0.0037</t>
-  </si>
-  <si>
-    <t>0.0057,0.0021,0.9941,0.0004</t>
-  </si>
-  <si>
-    <t>0.0018,0.1639,0.9813,0.0006</t>
-  </si>
-  <si>
-    <t>0.0293,0.0044,0.9760,0.0014</t>
-  </si>
-  <si>
-    <t>0.0047,0.1663,0.9731,0.0029</t>
-  </si>
-  <si>
-    <t>0.0497,0.0162,0.8971,0.0649</t>
-  </si>
-  <si>
-    <t>0.0265,0.0005,0.9859,0.0006</t>
-  </si>
-  <si>
-    <t>0.0313,0.0086,0.9705,0.0021</t>
-  </si>
-  <si>
-    <t>0.6351,0.0113,0.3879,0.0127</t>
-  </si>
-  <si>
-    <t>0.6188,0.0117,0.4733,0.0049</t>
-  </si>
-  <si>
-    <t>0.5955,0.0857,0.3579,0.0095</t>
-  </si>
-  <si>
-    <t>0.3410,0.0315,0.6627,0.0045</t>
-  </si>
-  <si>
-    <t>0.0281,0.6627,0.5153,0.0007</t>
-  </si>
-  <si>
-    <t>0.4211,0.0386,0.6112,0.0046</t>
-  </si>
-  <si>
-    <t>0.5963,0.0340,0.3945,0.0195</t>
-  </si>
-  <si>
-    <t>0.4042,0.0453,0.5866,0.0216</t>
-  </si>
-  <si>
-    <t>0.8142,0.2754,0.0101,0.0008</t>
-  </si>
-  <si>
-    <t>0.5342,0.6145,0.0094,0.0005</t>
-  </si>
-  <si>
-    <t>0.7334,0.4240,0.0029,0.0005</t>
-  </si>
-  <si>
-    <t>0.9604,0.0427,0.0073,0.0013</t>
-  </si>
-  <si>
-    <t>0.9228,0.1018,0.0101,0.0015</t>
-  </si>
-  <si>
-    <t>0.5107,0.0984,0.4144,0.0205</t>
-  </si>
-  <si>
-    <t>0.8736,0.0090,0.1125,0.0070</t>
-  </si>
-  <si>
-    <t>0.7319,0.0088,0.2872,0.0122</t>
-  </si>
-  <si>
-    <t>0.8196,0.0160,0.1648,0.0177</t>
-  </si>
-  <si>
-    <t>0.7973,0.0363,0.1006,0.0414</t>
-  </si>
-  <si>
-    <t>0.0112,0.0316,0.9441,0.0499</t>
-  </si>
-  <si>
-    <t>0.0196,0.1385,0.9168,0.0117</t>
-  </si>
-  <si>
-    <t>0.0287,0.0383,0.9477,0.0080</t>
-  </si>
-  <si>
-    <t>0.0546,0.0672,0.9121,0.0102</t>
-  </si>
-  <si>
-    <t>0.0319,0.3694,0.7816,0.0132</t>
-  </si>
-  <si>
-    <t>0.9768,0.0147,0.0033,0.0036</t>
-  </si>
-  <si>
-    <t>0.9721,0.0136,0.0102,0.0023</t>
-  </si>
-  <si>
-    <t>0.9838,0.0101,0.0014,0.0027</t>
-  </si>
-  <si>
-    <t>0.9284,0.0968,0.0079,0.0012</t>
-  </si>
-  <si>
-    <t>0.9779,0.0128,0.0053,0.0018</t>
-  </si>
-  <si>
-    <t>0.9856,0.0044,0.0018,0.0043</t>
-  </si>
-  <si>
-    <t>0.9927,0.0034,0.0003,0.0010</t>
-  </si>
-  <si>
-    <t>0.9815,0.0151,0.0030,0.0014</t>
-  </si>
-  <si>
-    <t>0.0298,0.0724,0.9272,0.0026</t>
-  </si>
-  <si>
-    <t>0.3833,0.0755,0.6199,0.0058</t>
-  </si>
-  <si>
-    <t>0.8488,0.0201,0.0389,0.0586</t>
-  </si>
-  <si>
-    <t>0.0027,0.0134,0.9944,0.0002</t>
-  </si>
-  <si>
-    <t>0.0009,0.0097,0.9973,0.0003</t>
-  </si>
-  <si>
-    <t>0.0175,0.0801,0.9586,0.0030</t>
-  </si>
-  <si>
-    <t>0.0000,0.0016,0.9995,0.0005</t>
-  </si>
-  <si>
-    <t>0.0581,0.0228,0.9193,0.0038</t>
-  </si>
-  <si>
-    <t>0.0090,0.0097,0.9877,0.0017</t>
-  </si>
-  <si>
-    <t>0.0058,0.0068,0.9873,0.0017</t>
-  </si>
-  <si>
-    <t>0.1708,0.0754,0.7543,0.0060</t>
-  </si>
-  <si>
-    <t>0.7885,0.0069,0.1872,0.0108</t>
-  </si>
-  <si>
-    <t>0.5080,0.0042,0.5493,0.0148</t>
-  </si>
-  <si>
-    <t>0.7482,0.0147,0.2843,0.0063</t>
-  </si>
-  <si>
-    <t>0.9868,0.0107,0.0017,0.0007</t>
-  </si>
-  <si>
-    <t>0.9813,0.0244,0.0015,0.0003</t>
-  </si>
-  <si>
-    <t>0.9927,0.0055,0.0007,0.0003</t>
-  </si>
-  <si>
-    <t>0.9814,0.0180,0.0024,0.0005</t>
-  </si>
-  <si>
-    <t>0.9812,0.0015,0.0005,0.0138</t>
-  </si>
-  <si>
-    <t>0.9807,0.0173,0.0036,0.0011</t>
-  </si>
-  <si>
-    <t>0.9834,0.0146,0.0015,0.0015</t>
-  </si>
-  <si>
-    <t>0.9711,0.0217,0.0039,0.0033</t>
-  </si>
-  <si>
-    <t>0.0681,0.0224,0.9157,0.0020</t>
-  </si>
-  <si>
-    <t>0.0023,0.0801,0.9848,0.0013</t>
-  </si>
-  <si>
-    <t>0.0096,0.0105,0.9803,0.0041</t>
-  </si>
-  <si>
-    <t>0.0594,0.0353,0.8873,0.0008</t>
-  </si>
-  <si>
-    <t>0.0338,0.0146,0.9496,0.0099</t>
-  </si>
-  <si>
-    <t>0.4058,0.0194,0.4758,0.1236</t>
-  </si>
-  <si>
-    <t>0.1511,0.0055,0.8854,0.0053</t>
-  </si>
-  <si>
-    <t>0.0508,0.1346,0.7813,0.1338</t>
-  </si>
-  <si>
-    <t>0.4010,0.0038,0.0082,0.7301</t>
-  </si>
-  <si>
-    <t>0.1660,0.1507,0.0178,0.8882</t>
-  </si>
-  <si>
-    <t>0.0132,0.0130,0.0064,0.9885</t>
-  </si>
-  <si>
-    <t>0.0011,0.0002,0.0005,0.9987</t>
-  </si>
-  <si>
-    <t>0.0080,0.0004,0.0008,0.9957</t>
-  </si>
-  <si>
-    <t>0.8175,0.0755,0.0856,0.0358</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0,1,0,1</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>0.8650,0.0103,0.0354,0.0552</t>
+  </si>
+  <si>
+    <t>0.0647,0.0035,0.0025,0.9757</t>
+  </si>
+  <si>
+    <t>0.6744,0.1112,0.0599,0.1984</t>
+  </si>
+  <si>
+    <t>0.0652,0.0017,0.0021,0.9790</t>
+  </si>
+  <si>
+    <t>0.9947,0.0045,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.9910,0.0028,0.0003,0.0014</t>
+  </si>
+  <si>
+    <t>0.9899,0.0059,0.0009,0.0008</t>
+  </si>
+  <si>
+    <t>0.9922,0.0034,0.0010,0.0010</t>
+  </si>
+  <si>
+    <t>0.9870,0.0054,0.0006,0.0025</t>
+  </si>
+  <si>
+    <t>0.9904,0.0084,0.0008,0.0007</t>
+  </si>
+  <si>
+    <t>0.9976,0.0007,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9917,0.0043,0.0007,0.0007</t>
+  </si>
+  <si>
+    <t>0.6655,0.0322,0.3077,0.0299</t>
+  </si>
+  <si>
+    <t>0.5526,0.0371,0.4574,0.0103</t>
+  </si>
+  <si>
+    <t>0.4050,0.0256,0.6202,0.0021</t>
+  </si>
+  <si>
+    <t>0.0595,0.0896,0.8555,0.0116</t>
+  </si>
+  <si>
+    <t>0.6162,0.0323,0.4014,0.0068</t>
+  </si>
+  <si>
+    <t>0.0051,0.9900,0.0014,0.0003</t>
+  </si>
+  <si>
+    <t>0.0443,0.9632,0.0044,0.0002</t>
+  </si>
+  <si>
+    <t>0.7132,0.3651,0.0257,0.0077</t>
+  </si>
+  <si>
+    <t>0.0126,0.9859,0.0019,0.0002</t>
+  </si>
+  <si>
+    <t>0.0062,0.9879,0.0051,0.0003</t>
+  </si>
+  <si>
+    <t>0.6393,0.0069,0.4020,0.0088</t>
+  </si>
+  <si>
+    <t>0.5631,0.0108,0.4699,0.0112</t>
+  </si>
+  <si>
+    <t>0.0332,0.0030,0.9764,0.0011</t>
+  </si>
+  <si>
+    <t>0.0947,0.0236,0.8734,0.0117</t>
+  </si>
+  <si>
+    <t>0.0219,0.0031,0.9750,0.0049</t>
+  </si>
+  <si>
+    <t>0.0098,0.0022,0.9871,0.0031</t>
+  </si>
+  <si>
+    <t>0.0160,0.0066,0.9564,0.0295</t>
+  </si>
+  <si>
+    <t>0.2996,0.6631,0.0780,0.0118</t>
+  </si>
+  <si>
+    <t>0.6579,0.2756,0.1177,0.0077</t>
+  </si>
+  <si>
+    <t>0.0004,0.0068,0.9924,0.0161</t>
+  </si>
+  <si>
+    <t>0.0185,0.9223,0.2006,0.0031</t>
+  </si>
+  <si>
+    <t>0.3957,0.4488,0.0124,0.1454</t>
+  </si>
+  <si>
+    <t>0.5438,0.2159,0.1888,0.0061</t>
+  </si>
+  <si>
+    <t>0.7868,0.2263,0.0360,0.0060</t>
+  </si>
+  <si>
+    <t>0.0466,0.9086,0.2526,0.0021</t>
+  </si>
+  <si>
+    <t>0.0472,0.1976,0.8551,0.0175</t>
+  </si>
+  <si>
+    <t>0.0710,0.0706,0.8462,0.0761</t>
+  </si>
+  <si>
+    <t>0.1133,0.0456,0.8604,0.0037</t>
+  </si>
+  <si>
+    <t>0.4595,0.0113,0.5148,0.0303</t>
+  </si>
+  <si>
+    <t>0.0270,0.0751,0.9311,0.0035</t>
+  </si>
+  <si>
+    <t>0.0030,0.9752,0.0815,0.0032</t>
+  </si>
+  <si>
+    <t>0.0835,0.0452,0.8780,0.0360</t>
+  </si>
+  <si>
+    <t>0.0042,0.9098,0.0056,0.8238</t>
+  </si>
+  <si>
+    <t>0.0030,0.9825,0.0347,0.0139</t>
+  </si>
+  <si>
+    <t>0.0017,0.9902,0.1024,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.9958,0.0698,0.0004</t>
+  </si>
+  <si>
+    <t>0.0225,0.0512,0.9505,0.0116</t>
+  </si>
+  <si>
+    <t>0.0017,0.1494,0.9861,0.0008</t>
+  </si>
+  <si>
+    <t>0.0132,0.0065,0.9840,0.0009</t>
+  </si>
+  <si>
+    <t>0.0297,0.0068,0.9694,0.0015</t>
+  </si>
+  <si>
+    <t>0.0144,0.0048,0.9846,0.0016</t>
+  </si>
+  <si>
+    <t>0.0201,0.0290,0.9625,0.0010</t>
+  </si>
+  <si>
+    <t>0.9506,0.0350,0.0052,0.0082</t>
+  </si>
+  <si>
+    <t>0.9849,0.0088,0.0024,0.0007</t>
+  </si>
+  <si>
+    <t>0.9635,0.0222,0.0132,0.0026</t>
+  </si>
+  <si>
+    <t>0.0043,0.0958,0.9785,0.0036</t>
+  </si>
+  <si>
+    <t>0.9773,0.0099,0.0070,0.0030</t>
+  </si>
+  <si>
+    <t>0.9921,0.0074,0.0009,0.0002</t>
+  </si>
+  <si>
+    <t>0.9800,0.0131,0.0034,0.0011</t>
+  </si>
+  <si>
+    <t>0.0020,0.7719,0.8575,0.0003</t>
+  </si>
+  <si>
+    <t>0.0138,0.0124,0.9457,0.0423</t>
+  </si>
+  <si>
+    <t>0.0035,0.0036,0.9845,0.0126</t>
+  </si>
+  <si>
+    <t>0.0001,0.8678,0.9842,0.0001</t>
+  </si>
+  <si>
+    <t>0.0026,0.0019,0.9957,0.0005</t>
+  </si>
+  <si>
+    <t>0.1056,0.7963,0.1223,0.0010</t>
+  </si>
+  <si>
+    <t>0.0391,0.9600,0.0055,0.0002</t>
+  </si>
+  <si>
+    <t>0.3688,0.2117,0.4931,0.0053</t>
+  </si>
+  <si>
+    <t>0.6781,0.1902,0.1513,0.0028</t>
+  </si>
+  <si>
+    <t>0.1080,0.5818,0.1806,0.0213</t>
+  </si>
+  <si>
+    <t>0.0002,0.8687,0.9627,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.7857,0.9430,0.0002</t>
+  </si>
+  <si>
+    <t>0.0006,0.9524,0.5936,0.0012</t>
+  </si>
+  <si>
+    <t>0.0045,0.5394,0.8918,0.0007</t>
+  </si>
+  <si>
+    <t>0.0752,0.0015,0.0231,0.9227</t>
+  </si>
+  <si>
+    <t>0.0080,0.0030,0.0008,0.9958</t>
+  </si>
+  <si>
+    <t>0.0026,0.0706,0.0012,0.9963</t>
+  </si>
+  <si>
+    <t>0.0046,0.0012,0.0008,0.9971</t>
+  </si>
+  <si>
+    <t>0.0163,0.0023,0.0072,0.9863</t>
+  </si>
+  <si>
+    <t>0.0060,0.0040,0.0011,0.9961</t>
+  </si>
+  <si>
+    <t>0.0028,0.8111,0.8781,0.0015</t>
+  </si>
+  <si>
+    <t>0.0049,0.7737,0.8931,0.0013</t>
+  </si>
+  <si>
+    <t>0.0185,0.5862,0.4959,0.0386</t>
+  </si>
+  <si>
+    <t>0.0114,0.4846,0.8714,0.0019</t>
+  </si>
+  <si>
+    <t>0.0019,0.8959,0.7164,0.0007</t>
+  </si>
+  <si>
+    <t>0.0011,0.6414,0.9478,0.0002</t>
+  </si>
+  <si>
+    <t>0.9864,0.0080,0.0020,0.0013</t>
+  </si>
+  <si>
+    <t>0.9763,0.0110,0.0026,0.0049</t>
+  </si>
+  <si>
+    <t>0.9847,0.0131,0.0030,0.0004</t>
+  </si>
+  <si>
+    <t>0.9840,0.0038,0.0012,0.0052</t>
+  </si>
+  <si>
+    <t>0.9881,0.0066,0.0014,0.0014</t>
+  </si>
+  <si>
+    <t>0.9940,0.0058,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.9828,0.0120,0.0022,0.0012</t>
+  </si>
+  <si>
+    <t>0.9846,0.0170,0.0018,0.0004</t>
+  </si>
+  <si>
+    <t>0.9922,0.0023,0.0007,0.0019</t>
+  </si>
+  <si>
+    <t>0.9916,0.0030,0.0004,0.0019</t>
+  </si>
+  <si>
+    <t>0.9964,0.0021,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9930,0.0023,0.0004,0.0013</t>
+  </si>
+  <si>
+    <t>0.9929,0.0050,0.0008,0.0005</t>
+  </si>
+  <si>
+    <t>0.9908,0.0055,0.0009,0.0008</t>
+  </si>
+  <si>
+    <t>0.9934,0.0015,0.0005,0.0014</t>
+  </si>
+  <si>
+    <t>0.9934,0.0016,0.0006,0.0013</t>
+  </si>
+  <si>
+    <t>0.0002,0.0006,0.9938,0.0113</t>
+  </si>
+  <si>
+    <t>0.1201,0.0040,0.9194,0.0035</t>
+  </si>
+  <si>
+    <t>0.5011,0.0219,0.4487,0.0433</t>
+  </si>
+  <si>
+    <t>0.2737,0.0045,0.8190,0.0006</t>
+  </si>
+  <si>
+    <t>0.1329,0.8886,0.0125,0.0003</t>
+  </si>
+  <si>
+    <t>0.0166,0.9760,0.0045,0.0005</t>
+  </si>
+  <si>
+    <t>0.0847,0.9234,0.0032,0.0013</t>
+  </si>
+  <si>
+    <t>0.1395,0.8893,0.0063,0.0004</t>
+  </si>
+  <si>
+    <t>0.3948,0.6756,0.0088,0.0059</t>
+  </si>
+  <si>
+    <t>0.0519,0.9441,0.0089,0.0010</t>
+  </si>
+  <si>
+    <t>0.6387,0.4642,0.0100,0.0031</t>
+  </si>
+  <si>
+    <t>0.4754,0.3334,0.2963,0.1339</t>
+  </si>
+  <si>
+    <t>0.2425,0.0269,0.7903,0.0044</t>
+  </si>
+  <si>
+    <t>0.1952,0.1717,0.6313,0.0298</t>
+  </si>
+  <si>
+    <t>0.3632,0.0283,0.6545,0.0048</t>
+  </si>
+  <si>
+    <t>0.0064,0.6524,0.0080,0.9520</t>
+  </si>
+  <si>
+    <t>0.0020,0.9887,0.0861,0.0009</t>
+  </si>
+  <si>
+    <t>0.0038,0.9764,0.0516,0.0230</t>
+  </si>
+  <si>
+    <t>0.0167,0.9439,0.0825,0.0290</t>
+  </si>
+  <si>
+    <t>0.0005,0.9712,0.6931,0.0015</t>
+  </si>
+  <si>
+    <t>0.0101,0.9844,0.0116,0.0001</t>
+  </si>
+  <si>
+    <t>0.7726,0.3282,0.0113,0.0005</t>
+  </si>
+  <si>
+    <t>0.4635,0.5483,0.0401,0.0010</t>
+  </si>
+  <si>
+    <t>0.9630,0.0221,0.0056,0.0074</t>
+  </si>
+  <si>
+    <t>0.9801,0.0105,0.0031,0.0037</t>
+  </si>
+  <si>
+    <t>0.9886,0.0037,0.0009,0.0027</t>
+  </si>
+  <si>
+    <t>0.9558,0.0226,0.0084,0.0112</t>
+  </si>
+  <si>
+    <t>0.9808,0.0053,0.0018,0.0067</t>
+  </si>
+  <si>
+    <t>0.9494,0.0346,0.0114,0.0099</t>
+  </si>
+  <si>
+    <t>0.9670,0.0111,0.0089,0.0076</t>
+  </si>
+  <si>
+    <t>0.9546,0.0272,0.0082,0.0068</t>
+  </si>
+  <si>
+    <t>0.0072,0.6159,0.8653,0.0009</t>
+  </si>
+  <si>
+    <t>0.0006,0.6877,0.9729,0.0001</t>
+  </si>
+  <si>
+    <t>0.0181,0.0649,0.9596,0.0052</t>
+  </si>
+  <si>
+    <t>0.0157,0.0397,0.9628,0.0060</t>
+  </si>
+  <si>
+    <t>0.6934,0.0368,0.2928,0.0157</t>
+  </si>
+  <si>
+    <t>0.5839,0.1041,0.2146,0.1727</t>
+  </si>
+  <si>
+    <t>0.3938,0.0049,0.7447,0.0026</t>
+  </si>
+  <si>
+    <t>0.6457,0.1588,0.1909,0.0075</t>
+  </si>
+  <si>
+    <t>0.0388,0.0041,0.0124,0.9725</t>
+  </si>
+  <si>
+    <t>0.0007,0.0002,0.0015,0.9984</t>
+  </si>
+  <si>
+    <t>0.0019,0.0029,0.0040,0.9964</t>
+  </si>
+  <si>
+    <t>0.0071,0.0005,0.0021,0.9945</t>
+  </si>
+  <si>
+    <t>0.0008,0.9888,0.1388,0.0007</t>
+  </si>
+  <si>
+    <t>0.9740,0.0133,0.0068,0.0028</t>
+  </si>
+  <si>
+    <t>0.1124,0.8564,0.0356,0.0106</t>
+  </si>
+  <si>
+    <t>0.8678,0.1308,0.0084,0.0215</t>
+  </si>
+  <si>
+    <t>0.8635,0.1202,0.0403,0.0049</t>
+  </si>
+  <si>
+    <t>0.9621,0.0205,0.0107,0.0026</t>
+  </si>
+  <si>
+    <t>0.5893,0.0165,0.1007,0.3085</t>
+  </si>
+  <si>
+    <t>0.9860,0.0043,0.0024,0.0015</t>
+  </si>
+  <si>
+    <t>0.0044,0.0146,0.9229,0.1982</t>
+  </si>
+  <si>
+    <t>0.9196,0.0053,0.0181,0.0326</t>
+  </si>
+  <si>
+    <t>0.9299,0.0101,0.0349,0.0149</t>
+  </si>
+  <si>
+    <t>0.4692,0.5166,0.0424,0.0254</t>
+  </si>
+  <si>
+    <t>0.8705,0.0733,0.0389,0.0078</t>
+  </si>
+  <si>
+    <t>0.8805,0.0873,0.0231,0.0032</t>
+  </si>
+  <si>
+    <t>0.3083,0.6093,0.1004,0.0885</t>
+  </si>
+  <si>
+    <t>0.6859,0.2769,0.0733,0.0127</t>
+  </si>
+  <si>
+    <t>0.8890,0.0568,0.0352,0.0075</t>
+  </si>
+  <si>
+    <t>0.9929,0.0029,0.0004,0.0009</t>
+  </si>
+  <si>
+    <t>0.9795,0.0100,0.0034,0.0041</t>
+  </si>
+  <si>
+    <t>0.9862,0.0028,0.0012,0.0064</t>
+  </si>
+  <si>
+    <t>0.9838,0.0049,0.0038,0.0033</t>
+  </si>
+  <si>
+    <t>0.9842,0.0045,0.0022,0.0043</t>
+  </si>
+  <si>
+    <t>0.9793,0.0053,0.0063,0.0040</t>
+  </si>
+  <si>
+    <t>0.9834,0.0053,0.0006,0.0061</t>
+  </si>
+  <si>
+    <t>0.9734,0.0115,0.0038,0.0060</t>
+  </si>
+  <si>
+    <t>0.5497,0.5110,0.0058,0.0057</t>
+  </si>
+  <si>
+    <t>0.7532,0.3227,0.0095,0.0005</t>
+  </si>
+  <si>
+    <t>0.5934,0.4407,0.0292,0.0014</t>
+  </si>
+  <si>
+    <t>0.0435,0.4462,0.7730,0.0034</t>
+  </si>
+  <si>
+    <t>0.9211,0.0976,0.0056,0.0034</t>
+  </si>
+  <si>
+    <t>0.8884,0.1057,0.0124,0.0059</t>
+  </si>
+  <si>
+    <t>0.9786,0.0113,0.0037,0.0016</t>
+  </si>
+  <si>
+    <t>0.9529,0.0216,0.0218,0.0028</t>
+  </si>
+  <si>
+    <t>0.0071,0.1845,0.9709,0.0010</t>
+  </si>
+  <si>
+    <t>0.9357,0.0867,0.0054,0.0011</t>
+  </si>
+  <si>
+    <t>0.0007,0.0033,0.9972,0.0007</t>
+  </si>
+  <si>
+    <t>0.0109,0.0203,0.9829,0.0012</t>
+  </si>
+  <si>
+    <t>0.0394,0.0311,0.9429,0.0022</t>
+  </si>
+  <si>
+    <t>0.0533,0.1961,0.8730,0.0093</t>
+  </si>
+  <si>
+    <t>0.0101,0.0029,0.9894,0.0008</t>
+  </si>
+  <si>
+    <t>0.0301,0.0041,0.9609,0.0099</t>
+  </si>
+  <si>
+    <t>0.0172,0.0017,0.9887,0.0002</t>
+  </si>
+  <si>
+    <t>0.4801,0.0306,0.5544,0.0090</t>
+  </si>
+  <si>
+    <t>0.3344,0.1093,0.6030,0.0453</t>
+  </si>
+  <si>
+    <t>0.6672,0.0227,0.3660,0.0091</t>
+  </si>
+  <si>
+    <t>0.1666,0.3612,0.4965,0.0048</t>
+  </si>
+  <si>
+    <t>0.3548,0.0798,0.5306,0.0018</t>
+  </si>
+  <si>
+    <t>0.5977,0.0585,0.3825,0.0128</t>
+  </si>
+  <si>
+    <t>0.4822,0.0370,0.5310,0.0144</t>
+  </si>
+  <si>
+    <t>0.4963,0.0255,0.5266,0.0149</t>
+  </si>
+  <si>
+    <t>0.7786,0.3494,0.0069,0.0009</t>
+  </si>
+  <si>
+    <t>0.7340,0.4291,0.0061,0.0004</t>
+  </si>
+  <si>
+    <t>0.7651,0.3710,0.0085,0.0012</t>
+  </si>
+  <si>
+    <t>0.9480,0.0539,0.0100,0.0018</t>
+  </si>
+  <si>
+    <t>0.9206,0.0581,0.0208,0.0075</t>
+  </si>
+  <si>
+    <t>0.2665,0.5728,0.1902,0.0397</t>
+  </si>
+  <si>
+    <t>0.6519,0.0064,0.4148,0.0088</t>
+  </si>
+  <si>
+    <t>0.6544,0.0145,0.2601,0.0546</t>
+  </si>
+  <si>
+    <t>0.6822,0.0074,0.3922,0.0015</t>
+  </si>
+  <si>
+    <t>0.5788,0.1732,0.1400,0.1654</t>
+  </si>
+  <si>
+    <t>0.0323,0.0113,0.9417,0.0303</t>
+  </si>
+  <si>
+    <t>0.1448,0.1305,0.7707,0.0421</t>
+  </si>
+  <si>
+    <t>0.0092,0.0735,0.9690,0.0014</t>
+  </si>
+  <si>
+    <t>0.1393,0.0114,0.8535,0.0181</t>
+  </si>
+  <si>
+    <t>0.0242,0.5236,0.6352,0.0113</t>
+  </si>
+  <si>
+    <t>0.9909,0.0024,0.0003,0.0028</t>
+  </si>
+  <si>
+    <t>0.9393,0.0496,0.0087,0.0128</t>
+  </si>
+  <si>
+    <t>0.9823,0.0083,0.0037,0.0031</t>
+  </si>
+  <si>
+    <t>0.9914,0.0072,0.0007,0.0006</t>
+  </si>
+  <si>
+    <t>0.9682,0.0213,0.0101,0.0030</t>
+  </si>
+  <si>
+    <t>0.9849,0.0093,0.0023,0.0014</t>
+  </si>
+  <si>
+    <t>0.9794,0.0048,0.0006,0.0065</t>
+  </si>
+  <si>
+    <t>0.9904,0.0072,0.0015,0.0006</t>
+  </si>
+  <si>
+    <t>0.0414,0.0176,0.9376,0.0222</t>
+  </si>
+  <si>
+    <t>0.6929,0.2251,0.1283,0.0232</t>
+  </si>
+  <si>
+    <t>0.9299,0.0299,0.0161,0.0172</t>
+  </si>
+  <si>
+    <t>0.0112,0.0043,0.9878,0.0006</t>
+  </si>
+  <si>
+    <t>0.0003,0.0103,0.9971,0.0009</t>
+  </si>
+  <si>
+    <t>0.0123,0.1978,0.9235,0.0006</t>
+  </si>
+  <si>
+    <t>0.0096,0.0061,0.9898,0.0006</t>
+  </si>
+  <si>
+    <t>0.0593,0.0044,0.9538,0.0020</t>
+  </si>
+  <si>
+    <t>0.0048,0.0035,0.9886,0.0037</t>
+  </si>
+  <si>
+    <t>0.0045,0.0029,0.9935,0.0004</t>
+  </si>
+  <si>
+    <t>0.0969,0.1228,0.7731,0.0213</t>
+  </si>
+  <si>
+    <t>0.7914,0.0016,0.1734,0.0106</t>
+  </si>
+  <si>
+    <t>0.4443,0.0088,0.3475,0.1227</t>
+  </si>
+  <si>
+    <t>0.5018,0.0086,0.5512,0.0180</t>
+  </si>
+  <si>
+    <t>0.9682,0.0474,0.0019,0.0002</t>
+  </si>
+  <si>
+    <t>0.9803,0.0157,0.0028,0.0018</t>
+  </si>
+  <si>
+    <t>0.9841,0.0091,0.0031,0.0018</t>
+  </si>
+  <si>
+    <t>0.9747,0.0200,0.0036,0.0019</t>
+  </si>
+  <si>
+    <t>0.9851,0.0050,0.0005,0.0044</t>
+  </si>
+  <si>
+    <t>0.9895,0.0097,0.0014,0.0002</t>
+  </si>
+  <si>
+    <t>0.9742,0.0215,0.0066,0.0011</t>
+  </si>
+  <si>
+    <t>0.9553,0.0346,0.0047,0.0056</t>
+  </si>
+  <si>
+    <t>0.0297,0.0959,0.9109,0.0010</t>
+  </si>
+  <si>
+    <t>0.0073,0.0434,0.9718,0.0057</t>
+  </si>
+  <si>
+    <t>0.0268,0.0558,0.9371,0.0045</t>
+  </si>
+  <si>
+    <t>0.0788,0.0816,0.8305,0.0045</t>
+  </si>
+  <si>
+    <t>0.0112,0.0091,0.9787,0.0048</t>
+  </si>
+  <si>
+    <t>0.1985,0.0149,0.7576,0.0672</t>
+  </si>
+  <si>
+    <t>0.2345,0.0374,0.7302,0.0270</t>
+  </si>
+  <si>
+    <t>0.1262,0.0914,0.8230,0.0096</t>
+  </si>
+  <si>
+    <t>0.8234,0.0019,0.0137,0.1239</t>
+  </si>
+  <si>
+    <t>0.0988,0.0601,0.0090,0.9473</t>
+  </si>
+  <si>
+    <t>0.0244,0.0141,0.0043,0.9866</t>
+  </si>
+  <si>
+    <t>0.0074,0.0009,0.0016,0.9949</t>
+  </si>
+  <si>
+    <t>0.0185,0.0005,0.0002,0.9947</t>
+  </si>
+  <si>
+    <t>0.5350,0.0723,0.0684,0.4425</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1968,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1970,7 +1982,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1981,10 +1993,10 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1998,7 +2010,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2024,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2038,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2052,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2066,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2080,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2094,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2108,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2122,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,7 +2136,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2135,10 +2147,10 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2152,7 +2164,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2166,7 +2178,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2180,7 +2192,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2206,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2220,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2219,10 +2231,10 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2248,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2262,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,7 +2276,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,7 +2290,7 @@
         <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2304,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,7 +2318,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2320,7 +2332,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2334,7 +2346,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2360,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2359,10 +2371,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,7 +2388,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2402,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2404,7 +2416,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2415,10 +2427,10 @@
         <v>259</v>
       </c>
       <c r="C35" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2429,10 +2441,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,7 +2458,7 @@
         <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2460,7 +2472,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2471,10 +2483,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2488,7 +2500,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2502,7 +2514,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,7 +2528,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2530,7 +2542,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2556,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2558,7 +2570,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2569,10 +2581,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2598,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2612,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2626,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,7 +2640,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,7 +2654,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,7 +2668,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2670,7 +2682,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2696,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,7 +2710,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2724,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2738,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2752,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2754,7 +2766,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2780,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2794,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2808,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,7 +2822,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2836,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2850,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,7 +2864,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2878,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,7 +2892,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2906,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2905,10 +2917,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2919,10 +2931,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2933,10 +2945,10 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2950,7 +2962,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2964,7 +2976,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2975,10 +2987,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,7 +3004,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3006,7 +3018,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3020,7 +3032,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3034,7 +3046,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3048,7 +3060,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3062,7 +3074,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3076,7 +3088,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,7 +3102,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,7 +3116,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3115,10 +3127,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3132,7 +3144,7 @@
         <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,7 +3158,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,7 +3172,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3186,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3200,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3214,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3228,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3242,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3256,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3270,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3284,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3298,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3312,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3326,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3340,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3354,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3368,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3382,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3396,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3410,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,7 +3424,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3423,10 +3435,10 @@
         <v>259</v>
       </c>
       <c r="C107" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3440,7 +3452,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3466,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3480,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3494,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,7 +3508,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3522,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3536,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,7 +3550,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3549,10 +3561,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,7 +3578,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3577,10 +3589,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3591,10 +3603,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3605,10 +3617,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3634,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3648,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3650,7 +3662,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,7 +3676,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3678,7 +3690,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3689,10 +3701,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3703,10 +3715,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3732,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3746,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3760,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3774,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3788,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3802,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3816,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3830,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3832,7 +3844,7 @@
         <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3843,10 +3855,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3857,10 +3869,10 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,7 +3886,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,7 +3900,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3899,10 +3911,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,7 +3928,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,7 +3942,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3944,7 +3956,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3958,7 +3970,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3972,7 +3984,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3986,7 +3998,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3997,10 +4009,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4026,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,7 +4040,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4054,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,7 +4068,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4082,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4081,10 +4093,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4110,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4124,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,7 +4138,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4152,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4151,10 +4163,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4180,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4194,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4193,10 +4205,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,7 +4222,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4236,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4250,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4264,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4278,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4292,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4306,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4320,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4334,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4348,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4347,10 +4359,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,7 +4376,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4375,10 +4387,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,7 +4404,7 @@
         <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4418,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4432,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4446,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4460,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4474,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4488,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4502,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4504,7 +4516,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4518,7 +4530,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,7 +4544,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4558,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4572,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4586,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4585,10 +4597,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4599,10 +4611,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4616,7 +4628,7 @@
         <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4627,10 +4639,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4641,10 +4653,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4655,10 +4667,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4669,10 +4681,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4686,7 +4698,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4700,7 +4712,7 @@
         <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4711,10 +4723,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,7 +4740,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4754,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,7 +4768,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4767,10 +4779,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4796,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,7 +4810,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,7 +4824,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,7 +4838,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4852,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4854,7 +4866,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4868,7 +4880,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4882,7 +4894,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4893,10 +4905,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4922,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4936,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4950,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4964,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4978,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4992,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +5006,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5020,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5022,7 +5034,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5033,10 +5045,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5062,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5076,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5090,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,7 +5104,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5118,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5120,7 +5132,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5146,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5160,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5162,7 +5174,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,7 +5188,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5187,10 +5199,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5201,10 +5213,10 @@
         <v>259</v>
       </c>
       <c r="C234" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5230,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5244,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5258,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5272,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5286,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5300,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5314,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5328,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5330,7 +5342,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5356,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,7 +5370,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5372,7 +5384,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5398,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5397,10 +5409,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5414,7 +5426,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5428,7 +5440,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5439,10 +5451,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5456,7 +5468,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5470,7 +5482,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5484,7 +5496,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5498,7 +5510,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,7 +5524,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>
